--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080562</v>
+        <v>125080509</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,7 +829,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363540</v>
+        <v>363530</v>
       </c>
       <c r="R3" t="n">
-        <v>6392666</v>
+        <v>6392676</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>Minst 2 ex flög förbi.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125080509</v>
+        <v>125080411</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,37 +928,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1001,24 +998,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex flög förbi.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,6 +1014,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1160,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125080411</v>
+        <v>125080562</v>
       </c>
       <c r="B6" t="n">
-        <v>8436</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,34 +1160,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1209,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363530</v>
+        <v>363540</v>
       </c>
       <c r="R6" t="n">
-        <v>6392676</v>
+        <v>6392666</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,14 +1233,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1259,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125080781</v>
+        <v>125080411</v>
       </c>
       <c r="B2" t="n">
-        <v>96729</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363618</v>
+        <v>363530</v>
       </c>
       <c r="R2" t="n">
-        <v>6392675</v>
+        <v>6392676</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +764,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera tuvor.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080509</v>
+        <v>125080781</v>
       </c>
       <c r="B3" t="n">
-        <v>57942</v>
+        <v>96729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,39 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363530</v>
+        <v>363618</v>
       </c>
       <c r="R3" t="n">
-        <v>6392676</v>
+        <v>6392675</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,24 +869,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 ex flög förbi.</t>
+          <t>Flera tuvor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125080411</v>
+        <v>125080509</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>57942</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,34 +916,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -998,14 +989,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Minst 2 ex flög förbi.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1015,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080614</v>
+        <v>125080562</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,33 +1045,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1081,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363565</v>
+        <v>363540</v>
       </c>
       <c r="R5" t="n">
-        <v>6392613</v>
+        <v>6392666</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,14 +1118,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några, vid vägen.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125080562</v>
+        <v>125080614</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,37 +1174,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1200,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363540</v>
+        <v>363565</v>
       </c>
       <c r="R6" t="n">
-        <v>6392666</v>
+        <v>6392613</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,24 +1243,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>Några, vid vägen.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125080411</v>
+        <v>125080562</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363530</v>
+        <v>363540</v>
       </c>
       <c r="R2" t="n">
-        <v>6392676</v>
+        <v>6392666</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,14 +760,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +786,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1033,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080562</v>
+        <v>125080411</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,37 +1057,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1085,13 +1094,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363540</v>
+        <v>363530</v>
       </c>
       <c r="R5" t="n">
-        <v>6392666</v>
+        <v>6392676</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,24 +1127,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,6 +1143,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125080562</v>
+        <v>125080509</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363540</v>
+        <v>363530</v>
       </c>
       <c r="R2" t="n">
-        <v>6392666</v>
+        <v>6392676</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>Minst 2 ex flög förbi.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080781</v>
+        <v>125080562</v>
       </c>
       <c r="B3" t="n">
-        <v>96729</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,31 +816,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363618</v>
+        <v>363540</v>
       </c>
       <c r="R3" t="n">
-        <v>6392675</v>
+        <v>6392666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,14 +889,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera tuvor.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +915,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125080509</v>
+        <v>125080411</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,37 +945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1001,24 +1015,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex flög förbi.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,6 +1031,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1045,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080411</v>
+        <v>125080614</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,30 +1066,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1094,10 +1098,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363530</v>
+        <v>363565</v>
       </c>
       <c r="R5" t="n">
-        <v>6392676</v>
+        <v>6392613</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1134,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Några, vid vägen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1147,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1162,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125080614</v>
+        <v>125080781</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>96729</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,31 +1181,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1210,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363565</v>
+        <v>363618</v>
       </c>
       <c r="R6" t="n">
-        <v>6392613</v>
+        <v>6392675</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,7 +1249,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Några, vid vägen.</t>
+          <t>Flera tuvor.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,6 +1258,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125080509</v>
+        <v>125080614</v>
       </c>
       <c r="B2" t="n">
-        <v>57942</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363530</v>
+        <v>363565</v>
       </c>
       <c r="R2" t="n">
-        <v>6392676</v>
+        <v>6392613</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,24 +756,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 2 ex flög förbi.</t>
+          <t>Några, vid vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -933,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125080411</v>
+        <v>125080509</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>57942</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,34 +931,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1015,14 +1004,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Minst 2 ex flög förbi.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1030,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1050,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080614</v>
+        <v>125080781</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>96729</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,31 +1064,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,13 +1092,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363565</v>
+        <v>363618</v>
       </c>
       <c r="R5" t="n">
-        <v>6392613</v>
+        <v>6392675</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några, vid vägen.</t>
+          <t>Flera tuvor.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1141,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125080781</v>
+        <v>125080411</v>
       </c>
       <c r="B6" t="n">
-        <v>96729</v>
+        <v>8436</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,27 +1176,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363618</v>
+        <v>363530</v>
       </c>
       <c r="R6" t="n">
-        <v>6392675</v>
+        <v>6392676</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera tuvor.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125080614</v>
+        <v>125080562</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363565</v>
+        <v>363540</v>
       </c>
       <c r="R2" t="n">
-        <v>6392613</v>
+        <v>6392666</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,14 +760,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Några, vid vägen.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080562</v>
+        <v>125080509</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,7 +846,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363540</v>
+        <v>363530</v>
       </c>
       <c r="R3" t="n">
-        <v>6392666</v>
+        <v>6392676</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +906,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>Minst 2 ex flög förbi.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125080509</v>
+        <v>125080781</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>96729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +945,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363530</v>
+        <v>363618</v>
       </c>
       <c r="R4" t="n">
-        <v>6392676</v>
+        <v>6392675</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,24 +1010,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex flög förbi.</t>
+          <t>Flera tuvor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1026,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1048,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080781</v>
+        <v>125080614</v>
       </c>
       <c r="B5" t="n">
-        <v>96729</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,27 +1061,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1092,13 +1093,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363618</v>
+        <v>363565</v>
       </c>
       <c r="R5" t="n">
-        <v>6392675</v>
+        <v>6392613</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,7 +1133,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera tuvor.</t>
+          <t>Några, vid vägen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1142,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125080562</v>
+        <v>125080509</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363540</v>
+        <v>363530</v>
       </c>
       <c r="R2" t="n">
-        <v>6392666</v>
+        <v>6392676</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>Minst 2 ex flög förbi.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080509</v>
+        <v>125080562</v>
       </c>
       <c r="B3" t="n">
-        <v>57942</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,7 +846,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -856,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363530</v>
+        <v>363540</v>
       </c>
       <c r="R3" t="n">
-        <v>6392676</v>
+        <v>6392666</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 ex flög förbi.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080614</v>
+        <v>125080411</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,29 +1061,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1093,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363565</v>
+        <v>363530</v>
       </c>
       <c r="R5" t="n">
-        <v>6392613</v>
+        <v>6392676</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,7 +1134,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några, vid vägen.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,6 +1143,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1160,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125080411</v>
+        <v>125080614</v>
       </c>
       <c r="B6" t="n">
-        <v>8436</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,30 +1178,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1209,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363530</v>
+        <v>363565</v>
       </c>
       <c r="R6" t="n">
-        <v>6392676</v>
+        <v>6392613</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1249,7 +1250,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Några, vid vägen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1259,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080562</v>
+        <v>125080614</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,37 +816,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -856,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363540</v>
+        <v>363565</v>
       </c>
       <c r="R3" t="n">
-        <v>6392666</v>
+        <v>6392613</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,24 +885,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>Några, vid vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1045,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080411</v>
+        <v>125080562</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,34 +1043,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1094,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363530</v>
+        <v>363540</v>
       </c>
       <c r="R5" t="n">
-        <v>6392676</v>
+        <v>6392666</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,14 +1116,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1142,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1162,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125080614</v>
+        <v>125080411</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>8436</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,29 +1176,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1210,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363565</v>
+        <v>363530</v>
       </c>
       <c r="R6" t="n">
-        <v>6392613</v>
+        <v>6392676</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1250,7 +1249,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Några, vid vägen.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,6 +1258,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125080509</v>
       </c>
       <c r="B2" t="n">
-        <v>57942</v>
+        <v>58060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080614</v>
+        <v>125080781</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>96897</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,31 +820,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,13 +848,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363565</v>
+        <v>363618</v>
       </c>
       <c r="R3" t="n">
-        <v>6392613</v>
+        <v>6392675</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Några, vid vägen.</t>
+          <t>Flera tuvor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,6 +897,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125080781</v>
+        <v>125080411</v>
       </c>
       <c r="B4" t="n">
-        <v>96729</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,27 +932,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363618</v>
+        <v>363530</v>
       </c>
       <c r="R4" t="n">
-        <v>6392675</v>
+        <v>6392676</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera tuvor.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080562</v>
+        <v>125080614</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,37 +1045,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1083,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363540</v>
+        <v>363565</v>
       </c>
       <c r="R5" t="n">
-        <v>6392666</v>
+        <v>6392613</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,24 +1114,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>Några, vid vägen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125080411</v>
+        <v>125080562</v>
       </c>
       <c r="B6" t="n">
-        <v>8436</v>
+        <v>57793</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,34 +1160,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1209,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363530</v>
+        <v>363540</v>
       </c>
       <c r="R6" t="n">
-        <v>6392676</v>
+        <v>6392666</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,14 +1233,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1259,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125080509</v>
+        <v>125080562</v>
       </c>
       <c r="B2" t="n">
-        <v>58060</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363530</v>
+        <v>363540</v>
       </c>
       <c r="R2" t="n">
-        <v>6392676</v>
+        <v>6392666</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 2 ex flög förbi.</t>
+          <t>Pågående bobygge i björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080781</v>
+        <v>125080614</v>
       </c>
       <c r="B3" t="n">
-        <v>96897</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,27 +820,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363618</v>
+        <v>363565</v>
       </c>
       <c r="R3" t="n">
-        <v>6392675</v>
+        <v>6392613</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera tuvor.</t>
+          <t>Några, vid vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +901,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125080411</v>
+        <v>125080781</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>96897</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,32 +935,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363530</v>
+        <v>363618</v>
       </c>
       <c r="R4" t="n">
-        <v>6392676</v>
+        <v>6392675</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På avbruten björk.</t>
+          <t>Flera tuvor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125080614</v>
+        <v>125080509</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
+        <v>58060</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,33 +1043,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1081,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363565</v>
+        <v>363530</v>
       </c>
       <c r="R5" t="n">
-        <v>6392613</v>
+        <v>6392676</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,14 +1116,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några, vid vägen.</t>
+          <t>Minst 2 ex flög förbi.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125080562</v>
+        <v>125080411</v>
       </c>
       <c r="B6" t="n">
-        <v>57793</v>
+        <v>8436</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,37 +1172,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1200,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363540</v>
+        <v>363530</v>
       </c>
       <c r="R6" t="n">
-        <v>6392666</v>
+        <v>6392676</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,24 +1242,14 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Pågående bobygge i björkhögstubbe.</t>
+          <t>På avbruten björk.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,6 +1258,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,6 +1250,121 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127800251</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bollebygd, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>363720</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6392829</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>127800251</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>127800251</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>127800251</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>127800251</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125080614</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>125080562</v>
       </c>
       <c r="B4" t="n">
-        <v>57811</v>
+        <v>58013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125080614</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>125080562</v>
       </c>
       <c r="B4" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125080614</v>
       </c>
       <c r="B3" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>125080562</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31942-2023 artfynd.xlsx
+++ b/artfynd/A 31942-2023 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>125080562</v>
       </c>
       <c r="B4" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
